--- a/tools/excel/anssi/systemes-industriels/anssi-systemes-industriels-mesures-detaillees.xlsx
+++ b/tools/excel/anssi/systemes-industriels/anssi-systemes-industriels-mesures-detaillees.xlsx
@@ -5629,7 +5629,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Privilégieruncloisonnementphysiqueentrelesautomatesdesécurité fonctionnelle (SIS) et les automates standards (BPCS)</t>
+          <t>Privilégier un cloisonnement physique entre les automates de sécurité fonctionnelle (SIS) et les automates standards (BPCS)</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -6913,7 +6913,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Consulterrégulièrementlesévénementsgénérésparleséquipements sans-fil</t>
+          <t>Consulter régulièrement les événements générés par les équipements sans-fil</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Appliqueretvérifier lesrèglesdebonnespratiquesdeprogrammation</t>
+          <t>Appliquer et vérifier les règles de bonnes pratiques de programmation</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
